--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
+        <v>11</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="I16" s="14">
         <v>12</v>
       </c>
-      <c r="H16" s="15">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="I16" s="14">
-        <v>10</v>
-      </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.130434782608</v>
+        <v>-88.990825688073</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>16.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J17" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K17" s="15">
-        <v>23.529411764705</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>90.909090909090</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-16</v>
+        <v>-6.896551724137</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G18" s="14">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.448979591836</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.417910447761</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="L18" s="15">
-        <v>100</v>
+        <v>90.625</v>
       </c>
       <c r="M18" s="15">
-        <v>43.589743589743</v>
+        <v>41.860465116279</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.330396475770</v>
+        <v>-75.502008032128</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>30</v>
+        <v>26.315789473684</v>
       </c>
       <c r="F19" s="14">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G19" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H19" s="15">
-        <v>16.049382716049</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="J19" s="14">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="K19" s="15">
-        <v>8.695652173913</v>
+        <v>10.447761194029</v>
       </c>
       <c r="L19" s="15">
-        <v>7.758620689655</v>
+        <v>12.121212121212</v>
       </c>
       <c r="M19" s="15">
-        <v>-20.886075949367</v>
+        <v>-16.384180790960</v>
       </c>
       <c r="N19" s="15">
-        <v>-55.830388692579</v>
+        <v>-55.421686746988</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1109,11 +1109,11 @@
       <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>100</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="14">
         <v>3</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.826086956521</v>
+        <v>-98.275862068965</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.631578947368</v>
+        <v>24.137931034482</v>
       </c>
       <c r="F21" s="17">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="H21" s="18">
-        <v>2.564102564102</v>
+        <v>5.405405405405</v>
       </c>
       <c r="I21" s="17">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="K21" s="18">
-        <v>0.456621004566</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L21" s="18">
-        <v>21.546961325966</v>
+        <v>23.671497584541</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.172413793103</v>
+        <v>-2.290076335877</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.316818774445</v>
+        <v>-71.396648044692</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>10</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>42.857142857142</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I22" s="14">
+        <v>13</v>
+      </c>
+      <c r="J22" s="14">
         <v>12</v>
       </c>
-      <c r="J22" s="14">
-        <v>11</v>
-      </c>
       <c r="K22" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-14.285714285714</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
         <v>400</v>
       </c>
       <c r="M23" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D24" s="14">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15">
-        <v>5.454545454545</v>
+        <v>29.787234042553</v>
       </c>
       <c r="F24" s="14">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G24" s="14">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H24" s="15">
-        <v>34.562211981566</v>
+        <v>27.314814814814</v>
       </c>
       <c r="I24" s="14">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="J24" s="14">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="K24" s="15">
-        <v>17.894736842105</v>
+        <v>18.975903614457</v>
       </c>
       <c r="L24" s="15">
-        <v>10.891089108910</v>
+        <v>6.756756756756</v>
       </c>
       <c r="M24" s="15">
-        <v>65.517241379310</v>
+        <v>72.489082969432</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E25" s="15">
-        <v>30.952380952381</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G25" s="14">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H25" s="15">
-        <v>51.807228915662</v>
+        <v>43.859649122807</v>
       </c>
       <c r="I25" s="14">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="J25" s="14">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="K25" s="15">
-        <v>30.875576036866</v>
+        <v>33.725490196078</v>
       </c>
       <c r="L25" s="15">
-        <v>6.766917293233</v>
+        <v>6.5625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
         <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J26" s="14">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.428571428571</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="L26" s="15">
-        <v>2.325581395348</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="M26" s="15">
-        <v>15.789473684210</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
-      </c>
-      <c r="F28" s="14">
-        <v>7</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
         <v>9</v>
       </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
       <c r="K28" s="15">
-        <v>28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,17 +1566,17 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -878,14 +878,14 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -901,196 +901,196 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <v>5</v>
       </c>
-      <c r="G15" s="14">
+      <c r="J15" s="15">
         <v>1</v>
       </c>
-      <c r="H15" s="15">
+      <c r="K15" s="14">
         <v>400</v>
       </c>
-      <c r="I15" s="14">
-        <v>5</v>
-      </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
-      <c r="K15" s="15">
+      <c r="L15" s="14">
         <v>400</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="15">
+      <c r="M15" s="14">
         <v>400</v>
       </c>
-      <c r="N15" s="15">
-        <v>150</v>
+      <c r="N15" s="14">
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14">
-        <v>7</v>
-      </c>
-      <c r="G16" s="14">
-        <v>11</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-36.363636363636</v>
-      </c>
-      <c r="I16" s="14">
-        <v>12</v>
-      </c>
-      <c r="J16" s="14">
-        <v>18</v>
-      </c>
-      <c r="K16" s="15">
+      <c r="C16" s="15">
+        <v>4</v>
+      </c>
+      <c r="D16" s="15">
+        <v>6</v>
+      </c>
+      <c r="E16" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="L16" s="15">
+      <c r="F16" s="15">
+        <v>9</v>
+      </c>
+      <c r="G16" s="15">
+        <v>15</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-40</v>
+      </c>
+      <c r="I16" s="15">
+        <v>16</v>
+      </c>
+      <c r="J16" s="15">
+        <v>24</v>
+      </c>
+      <c r="K16" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="M16" s="15">
-        <v>-45.454545454545</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-88.990825688073</v>
+      <c r="L16" s="14">
+        <v>-27.272727272727</v>
+      </c>
+      <c r="M16" s="14">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="N16" s="14">
+        <v>-87.401574803149</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <v>4</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <v>50</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <v>17</v>
       </c>
-      <c r="G17" s="14">
-        <v>15</v>
-      </c>
-      <c r="H17" s="15">
-        <v>13.333333333333</v>
-      </c>
-      <c r="I17" s="14">
-        <v>27</v>
-      </c>
-      <c r="J17" s="14">
-        <v>21</v>
-      </c>
-      <c r="K17" s="15">
-        <v>28.571428571428</v>
-      </c>
-      <c r="L17" s="15">
-        <v>28.571428571428</v>
-      </c>
-      <c r="M17" s="15">
-        <v>92.857142857142</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-6.896551724137</v>
+      <c r="G17" s="15">
+        <v>18</v>
+      </c>
+      <c r="H17" s="14">
+        <v>-5.555555555555</v>
+      </c>
+      <c r="I17" s="15">
+        <v>33</v>
+      </c>
+      <c r="J17" s="15">
+        <v>25</v>
+      </c>
+      <c r="K17" s="14">
+        <v>32</v>
+      </c>
+      <c r="L17" s="14">
+        <v>26.923076923076</v>
+      </c>
+      <c r="M17" s="14">
+        <v>135.714285714286</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>34</v>
-      </c>
-      <c r="G18" s="14">
-        <v>43</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-20.930232558139</v>
-      </c>
-      <c r="I18" s="14">
-        <v>61</v>
-      </c>
-      <c r="J18" s="14">
-        <v>71</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-14.084507042253</v>
-      </c>
-      <c r="L18" s="15">
-        <v>90.625</v>
-      </c>
-      <c r="M18" s="15">
-        <v>41.860465116279</v>
-      </c>
-      <c r="N18" s="15">
-        <v>-75.502008032128</v>
+      <c r="D18" s="15">
+        <v>6</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F18" s="15">
+        <v>21</v>
+      </c>
+      <c r="G18" s="15">
+        <v>28</v>
+      </c>
+      <c r="H18" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I18" s="15">
+        <v>65</v>
+      </c>
+      <c r="J18" s="15">
+        <v>77</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-15.584415584415</v>
+      </c>
+      <c r="L18" s="14">
+        <v>85.714285714285</v>
+      </c>
+      <c r="M18" s="14">
+        <v>30</v>
+      </c>
+      <c r="N18" s="14">
+        <v>-77.586206896551</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>24</v>
-      </c>
-      <c r="D19" s="14">
-        <v>19</v>
-      </c>
-      <c r="E19" s="15">
-        <v>26.315789473684</v>
-      </c>
-      <c r="F19" s="14">
-        <v>91</v>
-      </c>
-      <c r="G19" s="14">
-        <v>78</v>
-      </c>
-      <c r="H19" s="15">
-        <v>16.666666666666</v>
-      </c>
-      <c r="I19" s="14">
+      <c r="C19" s="15">
+        <v>21</v>
+      </c>
+      <c r="D19" s="15">
+        <v>14</v>
+      </c>
+      <c r="E19" s="14">
+        <v>50</v>
+      </c>
+      <c r="F19" s="15">
+        <v>89</v>
+      </c>
+      <c r="G19" s="15">
+        <v>77</v>
+      </c>
+      <c r="H19" s="14">
+        <v>15.584415584415</v>
+      </c>
+      <c r="I19" s="15">
+        <v>169</v>
+      </c>
+      <c r="J19" s="15">
         <v>148</v>
       </c>
-      <c r="J19" s="14">
-        <v>134</v>
-      </c>
-      <c r="K19" s="15">
-        <v>10.447761194029</v>
-      </c>
-      <c r="L19" s="15">
-        <v>12.121212121212</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-16.384180790960</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-55.421686746988</v>
+      <c r="K19" s="14">
+        <v>14.189189189189</v>
+      </c>
+      <c r="L19" s="14">
+        <v>19.858156028368</v>
+      </c>
+      <c r="M19" s="14">
+        <v>-17.961165048543</v>
+      </c>
+      <c r="N19" s="14">
+        <v>-55.759162303664</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,8 +1106,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>2</v>
+      <c r="F20" s="15">
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1115,23 +1115,23 @@
       <c r="H20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="15">
         <v>3</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="15">
         <v>3</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="14">
         <v>-25</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="14">
         <v>-40</v>
       </c>
-      <c r="N20" s="15">
-        <v>-98.275862068965</v>
+      <c r="N20" s="14">
+        <v>-98.514851485148</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>24.137931034482</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="G21" s="17">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H21" s="18">
-        <v>5.405405405405</v>
+        <v>1.438848920863</v>
       </c>
       <c r="I21" s="17">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>3.225806451612</v>
+        <v>4.676258992805</v>
       </c>
       <c r="L21" s="18">
-        <v>23.671497584541</v>
+        <v>26.521739130434</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.290076335877</v>
+        <v>-3.642384105960</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.396648044692</v>
+        <v>-71.965317919075</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="E22" s="14">
+        <v>100</v>
+      </c>
+      <c r="F22" s="15">
+        <v>10</v>
+      </c>
+      <c r="G22" s="15">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>100</v>
+      </c>
+      <c r="I22" s="15">
+        <v>15</v>
+      </c>
+      <c r="J22" s="15">
+        <v>13</v>
+      </c>
+      <c r="K22" s="14">
+        <v>15.384615384615</v>
+      </c>
+      <c r="L22" s="14">
         <v>0</v>
       </c>
-      <c r="F22" s="14">
-        <v>10</v>
-      </c>
-      <c r="G22" s="14">
-        <v>6</v>
-      </c>
-      <c r="H22" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="I22" s="14">
-        <v>13</v>
-      </c>
-      <c r="J22" s="14">
-        <v>12</v>
-      </c>
-      <c r="K22" s="15">
-        <v>8.333333333333</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-7.142857142857</v>
-      </c>
-      <c r="M22" s="15">
-        <v>85.714285714285</v>
+      <c r="M22" s="14">
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>4</v>
+      </c>
+      <c r="G23" s="15">
         <v>5</v>
       </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
-      <c r="H23" s="15">
-        <v>25</v>
-      </c>
-      <c r="I23" s="14">
+      <c r="H23" s="14">
+        <v>-20</v>
+      </c>
+      <c r="I23" s="15">
+        <v>6</v>
+      </c>
+      <c r="J23" s="15">
         <v>5</v>
       </c>
-      <c r="J23" s="14">
-        <v>4</v>
-      </c>
-      <c r="K23" s="15">
-        <v>25</v>
-      </c>
-      <c r="L23" s="15">
-        <v>400</v>
-      </c>
-      <c r="M23" s="15">
-        <v>66.666666666666</v>
+      <c r="K23" s="14">
+        <v>20</v>
+      </c>
+      <c r="L23" s="14">
+        <v>500</v>
+      </c>
+      <c r="M23" s="14">
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>61</v>
-      </c>
-      <c r="D24" s="14">
-        <v>47</v>
-      </c>
-      <c r="E24" s="15">
-        <v>29.787234042553</v>
-      </c>
-      <c r="F24" s="14">
-        <v>275</v>
-      </c>
-      <c r="G24" s="14">
-        <v>216</v>
-      </c>
-      <c r="H24" s="15">
-        <v>27.314814814814</v>
-      </c>
-      <c r="I24" s="14">
-        <v>395</v>
-      </c>
-      <c r="J24" s="14">
-        <v>332</v>
-      </c>
-      <c r="K24" s="15">
-        <v>18.975903614457</v>
-      </c>
-      <c r="L24" s="15">
-        <v>6.756756756756</v>
-      </c>
-      <c r="M24" s="15">
-        <v>72.489082969432</v>
+      <c r="C24" s="15">
+        <v>69</v>
+      </c>
+      <c r="D24" s="15">
+        <v>58</v>
+      </c>
+      <c r="E24" s="14">
+        <v>18.965517241379</v>
+      </c>
+      <c r="F24" s="15">
+        <v>272</v>
+      </c>
+      <c r="G24" s="15">
+        <v>209</v>
+      </c>
+      <c r="H24" s="14">
+        <v>30.143540669856</v>
+      </c>
+      <c r="I24" s="15">
+        <v>465</v>
+      </c>
+      <c r="J24" s="15">
+        <v>390</v>
+      </c>
+      <c r="K24" s="14">
+        <v>19.230769230769</v>
+      </c>
+      <c r="L24" s="14">
+        <v>6.896551724137</v>
+      </c>
+      <c r="M24" s="14">
+        <v>78.160919540229</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>57</v>
-      </c>
-      <c r="D25" s="14">
-        <v>38</v>
-      </c>
-      <c r="E25" s="15">
-        <v>50</v>
-      </c>
-      <c r="F25" s="14">
-        <v>246</v>
-      </c>
-      <c r="G25" s="14">
-        <v>171</v>
-      </c>
-      <c r="H25" s="15">
-        <v>43.859649122807</v>
-      </c>
-      <c r="I25" s="14">
-        <v>341</v>
-      </c>
-      <c r="J25" s="14">
-        <v>255</v>
-      </c>
-      <c r="K25" s="15">
-        <v>33.725490196078</v>
-      </c>
-      <c r="L25" s="15">
-        <v>6.5625</v>
+      <c r="C25" s="15">
+        <v>64</v>
+      </c>
+      <c r="D25" s="15">
+        <v>54</v>
+      </c>
+      <c r="E25" s="14">
+        <v>18.518518518518</v>
+      </c>
+      <c r="F25" s="15">
+        <v>247</v>
+      </c>
+      <c r="G25" s="15">
+        <v>178</v>
+      </c>
+      <c r="H25" s="14">
+        <v>38.764044943820</v>
+      </c>
+      <c r="I25" s="15">
+        <v>406</v>
+      </c>
+      <c r="J25" s="15">
+        <v>309</v>
+      </c>
+      <c r="K25" s="14">
+        <v>31.391585760517</v>
+      </c>
+      <c r="L25" s="14">
+        <v>7.692307692307</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>11</v>
-      </c>
-      <c r="D26" s="14">
-        <v>11</v>
-      </c>
-      <c r="E26" s="15">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14">
-        <v>30</v>
-      </c>
-      <c r="G26" s="14">
-        <v>40</v>
-      </c>
-      <c r="H26" s="15">
-        <v>-25</v>
-      </c>
-      <c r="I26" s="14">
-        <v>55</v>
-      </c>
-      <c r="J26" s="14">
-        <v>67</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-17.910447761194</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-6.779661016949</v>
-      </c>
-      <c r="M26" s="15">
-        <v>22.222222222222</v>
+      <c r="C26" s="15">
+        <v>14</v>
+      </c>
+      <c r="D26" s="15">
+        <v>8</v>
+      </c>
+      <c r="E26" s="14">
+        <v>75</v>
+      </c>
+      <c r="F26" s="15">
+        <v>38</v>
+      </c>
+      <c r="G26" s="15">
+        <v>37</v>
+      </c>
+      <c r="H26" s="14">
+        <v>2.702702702702</v>
+      </c>
+      <c r="I26" s="15">
+        <v>69</v>
+      </c>
+      <c r="J26" s="15">
+        <v>75</v>
+      </c>
+      <c r="K26" s="14">
+        <v>-8</v>
+      </c>
+      <c r="L26" s="14">
+        <v>-9.210526315789</v>
+      </c>
+      <c r="M26" s="14">
+        <v>40.816326530612</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="15">
+        <v>4</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <v>5</v>
       </c>
-      <c r="G27" s="14">
+      <c r="J27" s="15">
         <v>1</v>
       </c>
-      <c r="H27" s="15">
+      <c r="K27" s="14">
         <v>400</v>
       </c>
-      <c r="I27" s="14">
-        <v>5</v>
-      </c>
-      <c r="J27" s="14">
-        <v>1</v>
-      </c>
-      <c r="K27" s="15">
+      <c r="L27" s="14">
         <v>400</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>8</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>100</v>
-      </c>
-      <c r="I28" s="14">
-        <v>10</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
         <v>9</v>
       </c>
-      <c r="K28" s="15">
-        <v>11.111111111111</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-9.090909090909</v>
+      <c r="G28" s="15">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>50</v>
+      </c>
+      <c r="I28" s="15">
+        <v>12</v>
+      </c>
+      <c r="J28" s="15">
+        <v>12</v>
+      </c>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="14">
+        <v>-7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,14 +1493,14 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="14">
         <v>-100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1534,22 +1534,22 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="14">
         <v>-100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,7 +1557,7 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="15">
         <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
@@ -1566,17 +1566,17 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="14">
-        <v>2</v>
-      </c>
-      <c r="J31" s="14">
+      <c r="I31" s="15">
+        <v>3</v>
+      </c>
+      <c r="J31" s="15">
         <v>1</v>
       </c>
-      <c r="K31" s="15">
-        <v>100</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-33.333333333333</v>
+      <c r="K31" s="14">
+        <v>200</v>
+      </c>
+      <c r="L31" s="14">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>13</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="15">
         <v>6</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <v>2</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="15">
         <v>2</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="15">
         <v>2</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="14">
         <v>0</v>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="14">
         <v>0</v>
       </c>
-      <c r="M39" s="15">
+      <c r="M39" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="14">
         <v>-84.615384615384</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="14">
-        <v>21</v>
-      </c>
-      <c r="E40" s="14">
-        <v>21</v>
-      </c>
-      <c r="G40" s="14">
+      <c r="C40" s="15">
+        <v>21</v>
+      </c>
+      <c r="E40" s="15">
+        <v>21</v>
+      </c>
+      <c r="G40" s="15">
         <v>7</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="15">
         <v>10</v>
       </c>
-      <c r="J40" s="14">
-        <v>20</v>
-      </c>
-      <c r="K40" s="15">
+      <c r="J40" s="15">
+        <v>20</v>
+      </c>
+      <c r="K40" s="14">
         <v>100</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="14">
         <v>185.714285714286</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="14">
         <v>-4.761904761904</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="14">
         <v>-4.761904761904</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>1319</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="15">
         <v>1050</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <v>433</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="15">
         <v>308</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="15">
         <v>190</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>-38.311688311688</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="14">
         <v>-56.120092378752</v>
       </c>
-      <c r="M41" s="15">
+      <c r="M41" s="14">
         <v>-81.904761904761</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="14">
         <v>-85.595147839272</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>357</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="15">
         <v>303</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <v>205</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="15">
         <v>177</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="15">
         <v>284</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>60.451977401129</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="14">
         <v>38.536585365853</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="14">
         <v>-6.270627062706</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="14">
         <v>-20.448179271708</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>1986</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="15">
         <v>1649</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <v>692</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="15">
         <v>552</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J43" s="15">
         <v>380</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>-31.159420289855</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="14">
         <v>-45.086705202312</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="14">
         <v>-76.955730745906</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="14">
         <v>-80.866062437059</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>4632</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="15">
         <v>2765</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <v>1878</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="15">
         <v>1753</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J44" s="15">
         <v>1250</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>-28.693667997718</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="14">
         <v>-33.439829605963</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="14">
         <v>-54.792043399638</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="14">
         <v>-73.013816925734</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>1812</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="15">
         <v>1286</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <v>444</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="15">
         <v>216</v>
       </c>
-      <c r="J45" s="14">
+      <c r="J45" s="15">
         <v>53</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>-75.462962962963</v>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="14">
         <v>-88.063063063063</v>
       </c>
-      <c r="M45" s="15">
+      <c r="M45" s="14">
         <v>-95.878693623639</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="14">
         <v>-97.075055187638</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L15" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M15" s="14">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
+        <v>100</v>
+      </c>
+      <c r="F16" s="15">
+        <v>8</v>
+      </c>
+      <c r="G16" s="15">
+        <v>12</v>
+      </c>
+      <c r="H16" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="F16" s="15">
-        <v>9</v>
-      </c>
-      <c r="G16" s="15">
-        <v>15</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-40</v>
-      </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-33.333333333333</v>
+        <v>-28</v>
       </c>
       <c r="L16" s="14">
-        <v>-27.272727272727</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-38.461538461538</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.401574803149</v>
+        <v>-87.837837837837</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="14">
-        <v>-5.555555555555</v>
+        <v>-5</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>32</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>26.923076923076</v>
+        <v>42.307692307692</v>
       </c>
       <c r="M17" s="14">
-        <v>135.714285714286</v>
+        <v>146.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>0</v>
+        <v>5.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>10</v>
+      </c>
+      <c r="D18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
-        <v>6</v>
-      </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="15">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>15</v>
       </c>
       <c r="I18" s="15">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="J18" s="15">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K18" s="14">
-        <v>-15.584415584415</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="L18" s="14">
-        <v>85.714285714285</v>
+        <v>80.952380952380</v>
       </c>
       <c r="M18" s="14">
-        <v>30</v>
+        <v>24.590163934426</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.586206896551</v>
+        <v>-75.163398692810</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,45 +1060,45 @@
         <v>21</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F19" s="15">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" s="15">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H19" s="14">
-        <v>15.584415584415</v>
+        <v>37.878787878787</v>
       </c>
       <c r="I19" s="15">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J19" s="15">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K19" s="14">
-        <v>14.189189189189</v>
+        <v>18.012422360248</v>
       </c>
       <c r="L19" s="14">
-        <v>19.858156028368</v>
+        <v>23.376623376623</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.961165048543</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N19" s="14">
-        <v>-55.759162303664</v>
+        <v>-55.710955710955</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
       </c>
       <c r="K20" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="14">
-        <v>-25</v>
-      </c>
       <c r="M20" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.514851485148</v>
+        <v>-98.181818181818</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G21" s="17">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>1.438848920863</v>
+        <v>23.728813559322</v>
       </c>
       <c r="I21" s="17">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="J21" s="17">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="K21" s="18">
-        <v>4.676258992805</v>
+        <v>10.702341137123</v>
       </c>
       <c r="L21" s="18">
-        <v>26.521739130434</v>
+        <v>29.296875</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.642384105960</v>
+        <v>-0.301204819277</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.965317919075</v>
+        <v>-71.015761821366</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J22" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="14">
-        <v>15.384615384615</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1233,25 +1233,25 @@
         <v>4</v>
       </c>
       <c r="G23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
+        <v>7</v>
+      </c>
+      <c r="J23" s="15">
         <v>6</v>
       </c>
-      <c r="J23" s="15">
-        <v>5</v>
-      </c>
       <c r="K23" s="14">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M23" s="14">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D24" s="15">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" s="14">
-        <v>18.965517241379</v>
+        <v>13.559322033898</v>
       </c>
       <c r="F24" s="15">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="G24" s="15">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H24" s="14">
-        <v>30.143540669856</v>
+        <v>16.894977168949</v>
       </c>
       <c r="I24" s="15">
-        <v>465</v>
+        <v>530</v>
       </c>
       <c r="J24" s="15">
-        <v>390</v>
+        <v>449</v>
       </c>
       <c r="K24" s="14">
-        <v>19.230769230769</v>
+        <v>18.040089086859</v>
       </c>
       <c r="L24" s="14">
-        <v>6.896551724137</v>
+        <v>3.112840466926</v>
       </c>
       <c r="M24" s="14">
-        <v>78.160919540229</v>
+        <v>85.314685314685</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D25" s="15">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E25" s="14">
-        <v>18.518518518518</v>
+        <v>6.122448979591</v>
       </c>
       <c r="F25" s="15">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="G25" s="15">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H25" s="14">
-        <v>38.764044943820</v>
+        <v>25.136612021857</v>
       </c>
       <c r="I25" s="15">
-        <v>406</v>
+        <v>458</v>
       </c>
       <c r="J25" s="15">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="K25" s="14">
-        <v>31.391585760517</v>
+        <v>27.932960893854</v>
       </c>
       <c r="L25" s="14">
-        <v>7.692307692307</v>
+        <v>3.619909502262</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>75</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F26" s="15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>2.702702702702</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I26" s="15">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J26" s="15">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K26" s="14">
-        <v>-8</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L26" s="14">
-        <v>-9.210526315789</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M26" s="14">
-        <v>40.816326530612</v>
+        <v>40.740740740740</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>100</v>
       </c>
       <c r="F27" s="15">
         <v>4</v>
@@ -1403,16 +1403,16 @@
         <v>300</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="L27" s="14">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>11</v>
+      </c>
+      <c r="G28" s="15">
         <v>9</v>
       </c>
-      <c r="G28" s="15">
-        <v>6</v>
-      </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-7.692307692307</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,32 +1548,32 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L31" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,17 +892,17 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>500</v>
       </c>
       <c r="L15" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>-28</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="L16" s="14">
-        <v>-35.714285714285</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.931034482758</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.837837837837</v>
+        <v>-89.017341040462</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>4</v>
       </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K17" s="14">
-        <v>32.142857142857</v>
+        <v>21.875</v>
       </c>
       <c r="L17" s="14">
-        <v>42.307692307692</v>
+        <v>25.806451612903</v>
       </c>
       <c r="M17" s="14">
-        <v>146.666666666667</v>
+        <v>129.411764705882</v>
       </c>
       <c r="N17" s="14">
-        <v>5.714285714285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14">
-        <v>150</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F18" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H18" s="14">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="I18" s="15">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J18" s="15">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K18" s="14">
-        <v>-6.172839506172</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="L18" s="14">
-        <v>80.952380952380</v>
+        <v>68.085106382978</v>
       </c>
       <c r="M18" s="14">
-        <v>24.590163934426</v>
+        <v>12.857142857142</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.163398692810</v>
+        <v>-75.914634146341</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,57 +1057,57 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E19" s="14">
-        <v>61.538461538461</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="15">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" s="15">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H19" s="14">
-        <v>37.878787878787</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I19" s="15">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="J19" s="15">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="K19" s="14">
-        <v>18.012422360248</v>
+        <v>7.936507936507</v>
       </c>
       <c r="L19" s="14">
-        <v>23.376623376623</v>
+        <v>14.606741573033</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.636363636363</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="N19" s="14">
-        <v>-55.710955710955</v>
+        <v>-57.676348547717</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1131,7 +1131,7 @@
         <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.181818181818</v>
+        <v>-98.326359832636</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>85.714285714285</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H21" s="18">
-        <v>23.728813559322</v>
+        <v>4.838709677419</v>
       </c>
       <c r="I21" s="17">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="J21" s="17">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="K21" s="18">
-        <v>10.702341137123</v>
+        <v>2.332361516034</v>
       </c>
       <c r="L21" s="18">
-        <v>29.296875</v>
+        <v>19.387755102040</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.301204819277</v>
+        <v>-6.149732620320</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.015761821366</v>
+        <v>-72.274881516587</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K22" s="14">
-        <v>21.428571428571</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L22" s="14">
-        <v>6.25</v>
+        <v>18.75</v>
       </c>
       <c r="M22" s="14">
-        <v>41.666666666666</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15">
         <v>4</v>
       </c>
-      <c r="G23" s="15">
-        <v>6</v>
-      </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
         <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
         <v>600</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D24" s="15">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>13.559322033898</v>
+        <v>50</v>
       </c>
       <c r="F24" s="15">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G24" s="15">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H24" s="14">
-        <v>16.894977168949</v>
+        <v>27.619047619047</v>
       </c>
       <c r="I24" s="15">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="J24" s="15">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="K24" s="14">
-        <v>18.040089086859</v>
+        <v>21.212121212121</v>
       </c>
       <c r="L24" s="14">
-        <v>3.112840466926</v>
+        <v>7.719928186714</v>
       </c>
       <c r="M24" s="14">
-        <v>85.314685314685</v>
+        <v>94.174757281553</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D25" s="15">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E25" s="14">
-        <v>6.122448979591</v>
+        <v>60</v>
       </c>
       <c r="F25" s="15">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G25" s="15">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H25" s="14">
-        <v>25.136612021857</v>
+        <v>31.491712707182</v>
       </c>
       <c r="I25" s="15">
-        <v>458</v>
+        <v>522</v>
       </c>
       <c r="J25" s="15">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="K25" s="14">
-        <v>27.932960893854</v>
+        <v>31.155778894472</v>
       </c>
       <c r="L25" s="14">
-        <v>3.619909502262</v>
+        <v>10.828025477707</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>-46.153846153846</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H26" s="14">
-        <v>-19.047619047619</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="I26" s="15">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J26" s="15">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.636363636363</v>
+        <v>-19.417475728155</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.636363636363</v>
+        <v>-17</v>
       </c>
       <c r="M26" s="14">
-        <v>40.740740740740</v>
+        <v>25.757575757575</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
         <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="15">
+        <v>9</v>
+      </c>
+      <c r="G28" s="15">
         <v>11</v>
       </c>
-      <c r="G28" s="15">
-        <v>9</v>
-      </c>
       <c r="H28" s="14">
-        <v>22.222222222222</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L28" s="14">
-        <v>7.142857142857</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L15" s="14">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>-10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>-26.923076923076</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.709677419354</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-38.709677419354</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.017341040462</v>
+        <v>-87.939698492462</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>20</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I17" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J17" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K17" s="14">
-        <v>21.875</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="14">
-        <v>25.806451612903</v>
+        <v>18.421052631578</v>
       </c>
       <c r="M17" s="14">
-        <v>129.411764705882</v>
+        <v>164.705882352941</v>
       </c>
       <c r="N17" s="14">
-        <v>0</v>
+        <v>-8.163265306122</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>7</v>
+      </c>
+      <c r="D18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
-        <v>11</v>
-      </c>
       <c r="E18" s="14">
-        <v>-63.636363636363</v>
+        <v>75</v>
       </c>
       <c r="F18" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18" s="15">
         <v>25</v>
       </c>
       <c r="H18" s="14">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="I18" s="15">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J18" s="15">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18" s="14">
-        <v>-14.130434782608</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>68.085106382978</v>
+        <v>72</v>
       </c>
       <c r="M18" s="14">
-        <v>12.857142857142</v>
+        <v>21.126760563380</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.914634146341</v>
+        <v>-74.927113702623</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" s="15">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E19" s="14">
-        <v>-42.857142857142</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="F19" s="15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G19" s="15">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H19" s="14">
-        <v>8.108108108108</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="I19" s="15">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="J19" s="15">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="K19" s="14">
-        <v>7.936507936507</v>
+        <v>6.190476190476</v>
       </c>
       <c r="L19" s="14">
-        <v>14.606741573033</v>
+        <v>10.396039603960</v>
       </c>
       <c r="M19" s="14">
-        <v>-18.072289156626</v>
+        <v>-18.014705882352</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.676348547717</v>
+        <v>-57.197696737044</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
       </c>
       <c r="K20" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
         <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.326359832636</v>
+        <v>-97.65625</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-45.454545454545</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G21" s="17">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H21" s="18">
-        <v>4.838709677419</v>
+        <v>-1.492537313432</v>
       </c>
       <c r="I21" s="17">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="J21" s="17">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="K21" s="18">
-        <v>2.332361516034</v>
+        <v>2.094240837696</v>
       </c>
       <c r="L21" s="18">
-        <v>19.387755102040</v>
+        <v>17.824773413897</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.149732620320</v>
+        <v>-2.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.274881516587</v>
+        <v>-71.595047341587</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" s="14">
-        <v>5.555555555555</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L22" s="14">
-        <v>18.75</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M22" s="14">
-        <v>46.153846153846</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M23" s="14">
         <v>75</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E24" s="14">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F24" s="15">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G24" s="15">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H24" s="14">
-        <v>27.619047619047</v>
+        <v>23.943661971831</v>
       </c>
       <c r="I24" s="15">
-        <v>600</v>
+        <v>658</v>
       </c>
       <c r="J24" s="15">
-        <v>495</v>
+        <v>545</v>
       </c>
       <c r="K24" s="14">
-        <v>21.212121212121</v>
+        <v>20.733944954128</v>
       </c>
       <c r="L24" s="14">
-        <v>7.719928186714</v>
+        <v>4.278922345483</v>
       </c>
       <c r="M24" s="14">
-        <v>94.174757281553</v>
+        <v>86.931818181818</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E25" s="14">
-        <v>60</v>
+        <v>36.842105263157</v>
       </c>
       <c r="F25" s="15">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G25" s="15">
         <v>181</v>
       </c>
       <c r="H25" s="14">
-        <v>31.491712707182</v>
+        <v>28.176795580110</v>
       </c>
       <c r="I25" s="15">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="J25" s="15">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="K25" s="14">
-        <v>31.155778894472</v>
+        <v>31.651376146789</v>
       </c>
       <c r="L25" s="14">
-        <v>10.828025477707</v>
+        <v>6.691449814126</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,13 +1344,13 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
         <v>39</v>
@@ -1362,19 +1362,19 @@
         <v>-17.021276595744</v>
       </c>
       <c r="I26" s="15">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J26" s="15">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K26" s="14">
-        <v>-19.417475728155</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="L26" s="14">
-        <v>-17</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="M26" s="14">
-        <v>25.757575757575</v>
+        <v>22.368421052631</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
@@ -1397,19 +1397,19 @@
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="L27" s="14">
         <v>75</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="15">
         <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I28" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>-5.555555555555</v>
+        <v>-5</v>
       </c>
       <c r="L28" s="14">
-        <v>21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
         <v>-33.333333333333</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>-22.580645161290</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M16" s="14">
-        <v>-27.272727272727</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.939698492462</v>
+        <v>-88.095238095238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-37.5</v>
+        <v>75</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
         <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>12.5</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L17" s="14">
-        <v>18.421052631578</v>
+        <v>15.555555555555</v>
       </c>
       <c r="M17" s="14">
-        <v>164.705882352941</v>
+        <v>147.619047619048</v>
       </c>
       <c r="N17" s="14">
-        <v>-8.163265306122</v>
+        <v>-1.886792452830</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>75</v>
+        <v>-37.5</v>
       </c>
       <c r="F18" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H18" s="14">
-        <v>-4</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I18" s="15">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J18" s="15">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K18" s="14">
-        <v>-10.416666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="L18" s="14">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M18" s="14">
-        <v>21.126760563380</v>
+        <v>13.75</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.927113702623</v>
+        <v>-74.651810584958</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="14">
-        <v>-9.523809523809</v>
+        <v>25</v>
       </c>
       <c r="F19" s="15">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G19" s="15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H19" s="14">
-        <v>-1.315789473684</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="I19" s="15">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="J19" s="15">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="K19" s="14">
-        <v>6.190476190476</v>
+        <v>7.826086956521</v>
       </c>
       <c r="L19" s="14">
-        <v>10.396039603960</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M19" s="14">
-        <v>-18.014705882352</v>
+        <v>-17.607973421926</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.197696737044</v>
+        <v>-56.567425569176</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="14">
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>50</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M20" s="14">
         <v>20</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.65625</v>
+        <v>-97.887323943662</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>41</v>
+      </c>
+      <c r="D21" s="17">
         <v>38</v>
       </c>
-      <c r="D21" s="17">
-        <v>39</v>
-      </c>
       <c r="E21" s="18">
-        <v>-2.564102564102</v>
+        <v>7.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.492537313432</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="I21" s="17">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="J21" s="17">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="K21" s="18">
-        <v>2.094240837696</v>
+        <v>2.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>17.824773413897</v>
+        <v>18.508287292817</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.5</v>
+        <v>-3.595505617977</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.595047341587</v>
+        <v>-71.072151045178</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J22" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K22" s="14">
-        <v>-4.761904761904</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L22" s="14">
-        <v>17.647058823529</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M22" s="14">
-        <v>53.846153846153</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15">
         <v>2</v>
       </c>
-      <c r="G23" s="15">
-        <v>3</v>
-      </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
         <v>7</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>45</v>
+      </c>
+      <c r="D24" s="15">
         <v>58</v>
       </c>
-      <c r="D24" s="15">
-        <v>50</v>
-      </c>
       <c r="E24" s="14">
-        <v>16</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="F24" s="15">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="G24" s="15">
         <v>213</v>
       </c>
       <c r="H24" s="14">
-        <v>23.943661971831</v>
+        <v>13.145539906103</v>
       </c>
       <c r="I24" s="15">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="J24" s="15">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="K24" s="14">
-        <v>20.733944954128</v>
+        <v>16.583747927031</v>
       </c>
       <c r="L24" s="14">
-        <v>4.278922345483</v>
+        <v>-0.985915492957</v>
       </c>
       <c r="M24" s="14">
-        <v>86.931818181818</v>
+        <v>86.472148541114</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D25" s="15">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>36.842105263157</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F25" s="15">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="G25" s="15">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="H25" s="14">
-        <v>28.176795580110</v>
+        <v>18.604651162790</v>
       </c>
       <c r="I25" s="15">
-        <v>574</v>
+        <v>610</v>
       </c>
       <c r="J25" s="15">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="K25" s="14">
-        <v>31.651376146789</v>
+        <v>26.819126819126</v>
       </c>
       <c r="L25" s="14">
-        <v>6.691449814126</v>
+        <v>0.164203612479</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="15">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H26" s="14">
-        <v>-17.021276595744</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J26" s="15">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.421052631578</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.216216216216</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>22.368421052631</v>
+        <v>26.506024096385</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="15">
         <v>2</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
+        <v>9</v>
+      </c>
+      <c r="J27" s="15">
         <v>7</v>
       </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
       <c r="K27" s="14">
-        <v>40</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="14">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>-9.090909090909</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="14">
-        <v>-5</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
       <c r="E15" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L15" s="14">
         <v>250</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="14">
-        <v>-24.242424242424</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="14">
-        <v>-24.242424242424</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.555555555555</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.095238095238</v>
+        <v>-87.931034482758</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>18.181818181818</v>
+        <v>3.773584905660</v>
       </c>
       <c r="L17" s="14">
-        <v>15.555555555555</v>
+        <v>14.583333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>147.619047619048</v>
+        <v>111.538461538462</v>
       </c>
       <c r="N17" s="14">
-        <v>-1.886792452830</v>
+        <v>-5.172413793103</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
         <v>5</v>
       </c>
-      <c r="D18" s="15">
-        <v>8</v>
-      </c>
       <c r="E18" s="14">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="15">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G18" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" s="14">
-        <v>-7.407407407407</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I18" s="15">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J18" s="15">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K18" s="14">
-        <v>-12.5</v>
+        <v>-13.761467889908</v>
       </c>
       <c r="L18" s="14">
-        <v>82</v>
+        <v>80.769230769230</v>
       </c>
       <c r="M18" s="14">
-        <v>13.75</v>
+        <v>8.045977011494</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.651810584958</v>
+        <v>-75.647668393782</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,60 +1060,60 @@
         <v>25</v>
       </c>
       <c r="D19" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" s="14">
-        <v>25</v>
+        <v>38.888888888888</v>
       </c>
       <c r="F19" s="15">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G19" s="15">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H19" s="14">
-        <v>-4.878048780487</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="I19" s="15">
+        <v>274</v>
+      </c>
+      <c r="J19" s="15">
         <v>248</v>
       </c>
-      <c r="J19" s="15">
-        <v>230</v>
-      </c>
       <c r="K19" s="14">
-        <v>7.826086956521</v>
+        <v>10.483870967741</v>
       </c>
       <c r="L19" s="14">
-        <v>10.714285714285</v>
+        <v>13.223140495867</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.607973421926</v>
+        <v>-19.174041297935</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.567425569176</v>
+        <v>-56.16</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F20" s="15">
-        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
@@ -1125,13 +1125,13 @@
         <v>20</v>
       </c>
       <c r="L20" s="14">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.887323943662</v>
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>7.894736842105</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G21" s="17">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.225352112676</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="I21" s="17">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="J21" s="17">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="K21" s="18">
-        <v>2.142857142857</v>
+        <v>1.978021978021</v>
       </c>
       <c r="L21" s="18">
-        <v>18.508287292817</v>
+        <v>19.896640826873</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.595505617977</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.072151045178</v>
+        <v>-71.233725976441</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,13 +1180,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
       <c r="E22" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F22" s="15">
         <v>5</v>
@@ -1198,19 +1198,19 @@
         <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J22" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" s="14">
-        <v>-4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>29.411764705882</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="15">
         <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="15">
         <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="14">
         <v>250</v>
       </c>
       <c r="M23" s="14">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D24" s="15">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E24" s="14">
-        <v>-22.413793103448</v>
+        <v>5</v>
       </c>
       <c r="F24" s="15">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="G24" s="15">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="H24" s="14">
-        <v>13.145539906103</v>
+        <v>11.340206185567</v>
       </c>
       <c r="I24" s="15">
-        <v>703</v>
+        <v>746</v>
       </c>
       <c r="J24" s="15">
-        <v>603</v>
+        <v>643</v>
       </c>
       <c r="K24" s="14">
-        <v>16.583747927031</v>
+        <v>16.018662519440</v>
       </c>
       <c r="L24" s="14">
-        <v>-0.985915492957</v>
+        <v>-2.990897269180</v>
       </c>
       <c r="M24" s="14">
-        <v>86.472148541114</v>
+        <v>82.396088019559</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D25" s="15">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E25" s="14">
-        <v>-22.222222222222</v>
+        <v>12.121212121212</v>
       </c>
       <c r="F25" s="15">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="G25" s="15">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H25" s="14">
-        <v>18.604651162790</v>
+        <v>22.435897435897</v>
       </c>
       <c r="I25" s="15">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="J25" s="15">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="K25" s="14">
-        <v>26.819126819126</v>
+        <v>26.264591439688</v>
       </c>
       <c r="L25" s="14">
-        <v>0.164203612479</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G26" s="15">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H26" s="14">
-        <v>-33.333333333333</v>
+        <v>-18</v>
       </c>
       <c r="I26" s="15">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J26" s="15">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.604651162790</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.666666666666</v>
+        <v>-13.970588235294</v>
       </c>
       <c r="M26" s="14">
-        <v>26.506024096385</v>
+        <v>34.482758620689</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
-      </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L27" s="14">
         <v>125</v>
@@ -1429,31 +1429,31 @@
         <v>4</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J28" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K28" s="14">
-        <v>9.523809523809</v>
+        <v>8</v>
       </c>
       <c r="L28" s="14">
-        <v>4.545454545454</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -905,19 +905,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="14">
         <v>250</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I16" s="15">
         <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K16" s="14">
+        <v>-28.205128205128</v>
+      </c>
+      <c r="L16" s="14">
         <v>-20</v>
       </c>
-      <c r="L16" s="14">
-        <v>-17.647058823529</v>
-      </c>
       <c r="M16" s="14">
-        <v>-36.363636363636</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.931034482758</v>
+        <v>-88.524590163934</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H17" s="14">
-        <v>-28</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I17" s="15">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J17" s="15">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K17" s="14">
-        <v>3.773584905660</v>
+        <v>3.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>14.583333333333</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M17" s="14">
-        <v>111.538461538462</v>
+        <v>121.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-5.172413793103</v>
+        <v>5.084745762711</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
         <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>-32.142857142857</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I18" s="15">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J18" s="15">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K18" s="14">
-        <v>-13.761467889908</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L18" s="14">
-        <v>80.769230769230</v>
+        <v>80</v>
       </c>
       <c r="M18" s="14">
-        <v>8.045977011494</v>
+        <v>11.235955056179</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.647668393782</v>
+        <v>-75.970873786407</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D19" s="15">
         <v>18</v>
       </c>
       <c r="E19" s="14">
-        <v>38.888888888888</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G19" s="15">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.298850574712</v>
+        <v>16.883116883116</v>
       </c>
       <c r="I19" s="15">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="J19" s="15">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="K19" s="14">
-        <v>10.483870967741</v>
+        <v>10.902255639097</v>
       </c>
       <c r="L19" s="14">
-        <v>13.223140495867</v>
+        <v>16.141732283464</v>
       </c>
       <c r="M19" s="14">
-        <v>-19.174041297935</v>
+        <v>-17.597765363128</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.16</v>
+        <v>-56.489675516224</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="14">
         <v>-25</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.039215686274</v>
+        <v>-98.192771084337</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.857142857142</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="F21" s="17">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.461538461538</v>
+        <v>-3.355704697986</v>
       </c>
       <c r="I21" s="17">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="J21" s="17">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="K21" s="18">
-        <v>1.978021978021</v>
+        <v>1.016260162601</v>
       </c>
       <c r="L21" s="18">
-        <v>19.896640826873</v>
+        <v>22.113022113022</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.936507936507</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.233725976441</v>
+        <v>-71.288272674754</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="15">
         <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I22" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J22" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K22" s="14">
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>42.105263157894</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="15">
         <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M23" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D24" s="15">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E24" s="14">
-        <v>5</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="F24" s="15">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="G24" s="15">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H24" s="14">
-        <v>11.340206185567</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="I24" s="15">
-        <v>746</v>
+        <v>795</v>
       </c>
       <c r="J24" s="15">
-        <v>643</v>
+        <v>700</v>
       </c>
       <c r="K24" s="14">
-        <v>16.018662519440</v>
+        <v>13.571428571428</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.990897269180</v>
+        <v>-2.093596059113</v>
       </c>
       <c r="M24" s="14">
-        <v>82.396088019559</v>
+        <v>77.852348993288</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D25" s="15">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E25" s="14">
-        <v>12.121212121212</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="F25" s="15">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="G25" s="15">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H25" s="14">
-        <v>22.435897435897</v>
+        <v>2.469135802469</v>
       </c>
       <c r="I25" s="15">
-        <v>649</v>
+        <v>688</v>
       </c>
       <c r="J25" s="15">
-        <v>514</v>
+        <v>560</v>
       </c>
       <c r="K25" s="14">
-        <v>26.264591439688</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L25" s="14">
-        <v>-1.666666666666</v>
+        <v>-1.291248206599</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G26" s="15">
         <v>50</v>
       </c>
       <c r="H26" s="14">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="15">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J26" s="15">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.217391304347</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.970588235294</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>34.482758620689</v>
+        <v>31.632653061224</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,10 +1406,10 @@
         <v>9</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>125</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>20</v>
+        <v>62.5</v>
       </c>
       <c r="I28" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J28" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" s="14">
-        <v>8</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L28" s="14">
-        <v>12.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="14">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-30.769230769230</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K16" s="14">
-        <v>-28.205128205128</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L16" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.666666666666</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.524590163934</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
         <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-14.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-21.428571428571</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="I17" s="15">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K17" s="14">
-        <v>3.333333333333</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="L17" s="14">
-        <v>19.230769230769</v>
+        <v>20.370370370370</v>
       </c>
       <c r="M17" s="14">
-        <v>121.428571428571</v>
+        <v>124.137931034483</v>
       </c>
       <c r="N17" s="14">
-        <v>5.084745762711</v>
+        <v>-7.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-9.090909090909</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="15">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J18" s="15">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K18" s="14">
-        <v>-13.157894736842</v>
+        <v>-11.965811965812</v>
       </c>
       <c r="L18" s="14">
-        <v>80</v>
+        <v>83.928571428571</v>
       </c>
       <c r="M18" s="14">
-        <v>11.235955056179</v>
+        <v>10.752688172043</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.970873786407</v>
+        <v>-76.643990929705</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G19" s="15">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="14">
-        <v>16.883116883116</v>
+        <v>21.126760563380</v>
       </c>
       <c r="I19" s="15">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="J19" s="15">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="K19" s="14">
-        <v>10.902255639097</v>
+        <v>10.320284697508</v>
       </c>
       <c r="L19" s="14">
-        <v>16.141732283464</v>
+        <v>13.970588235294</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.597765363128</v>
+        <v>-21.319796954314</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.489675516224</v>
+        <v>-56.582633053221</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="14">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M20" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.192771084337</v>
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.216216216216</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="F21" s="17">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.355704697986</v>
+        <v>-4.316546762589</v>
       </c>
       <c r="I21" s="17">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="J21" s="17">
-        <v>492</v>
+        <v>521</v>
       </c>
       <c r="K21" s="18">
-        <v>1.016260162601</v>
+        <v>0.191938579654</v>
       </c>
       <c r="L21" s="18">
-        <v>22.113022113022</v>
+        <v>20.276497695852</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.578947368421</v>
+        <v>-9.532062391681</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.288272674754</v>
+        <v>-71.829465731246</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>-44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J22" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>42.105263157894</v>
+        <v>52.631578947368</v>
       </c>
       <c r="M22" s="14">
-        <v>28.571428571428</v>
+        <v>20.833333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1265,34 +1265,34 @@
         <v>50</v>
       </c>
       <c r="D24" s="15">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E24" s="14">
-        <v>-12.280701754386</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F24" s="15">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G24" s="15">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.878048780487</v>
+        <v>-2.590673575129</v>
       </c>
       <c r="I24" s="15">
-        <v>795</v>
+        <v>846</v>
       </c>
       <c r="J24" s="15">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="K24" s="14">
-        <v>13.571428571428</v>
+        <v>14.634146341463</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.093596059113</v>
+        <v>-2.870264064293</v>
       </c>
       <c r="M24" s="14">
-        <v>77.852348993288</v>
+        <v>76.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D25" s="15">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E25" s="14">
-        <v>-15.217391304347</v>
+        <v>44</v>
       </c>
       <c r="F25" s="15">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="G25" s="15">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H25" s="14">
-        <v>2.469135802469</v>
+        <v>0.671140939597</v>
       </c>
       <c r="I25" s="15">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="J25" s="15">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="K25" s="14">
-        <v>22.857142857142</v>
+        <v>23.931623931623</v>
       </c>
       <c r="L25" s="14">
-        <v>-1.291248206599</v>
+        <v>-2.027027027027</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-13.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>-4</v>
+        <v>16.279069767441</v>
       </c>
       <c r="I26" s="15">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J26" s="15">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.686274509803</v>
+        <v>-9.554140127388</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.416666666666</v>
+        <v>-8.387096774193</v>
       </c>
       <c r="M26" s="14">
-        <v>31.632653061224</v>
+        <v>22.413793103448</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>62.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="15">
         <v>32</v>
       </c>
       <c r="J28" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K28" s="14">
-        <v>23.076923076923</v>
+        <v>10.344827586206</v>
       </c>
       <c r="L28" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="15">
         <v>1</v>
       </c>
       <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
         <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M15" s="14">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="14">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -952,22 +952,22 @@
         <v>-30</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K16" s="14">
-        <v>-26.829268292682</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M16" s="14">
-        <v>-42.307692307692</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.679245283018</v>
+        <v>-88.489208633093</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-57.142857142857</v>
+        <v>60</v>
       </c>
       <c r="F17" s="15">
         <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H17" s="14">
-        <v>-25.925925925925</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J17" s="15">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K17" s="14">
-        <v>-2.985074626865</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>20.370370370370</v>
+        <v>30.909090909090</v>
       </c>
       <c r="M17" s="14">
-        <v>124.137931034483</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N17" s="14">
-        <v>-7.142857142857</v>
+        <v>-2.702702702702</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="14">
-        <v>-19.047619047619</v>
+        <v>-5</v>
       </c>
       <c r="I18" s="15">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J18" s="15">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K18" s="14">
-        <v>-11.965811965812</v>
+        <v>-10.483870967741</v>
       </c>
       <c r="L18" s="14">
-        <v>83.928571428571</v>
+        <v>88.135593220339</v>
       </c>
       <c r="M18" s="14">
-        <v>10.752688172043</v>
+        <v>15.625</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.643990929705</v>
+        <v>-76.680672268907</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="15">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G19" s="15">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H19" s="14">
-        <v>21.126760563380</v>
+        <v>6.410256410256</v>
       </c>
       <c r="I19" s="15">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="J19" s="15">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="K19" s="14">
-        <v>10.320284697508</v>
+        <v>8.116883116883</v>
       </c>
       <c r="L19" s="14">
-        <v>13.970588235294</v>
+        <v>15.224913494809</v>
       </c>
       <c r="M19" s="14">
-        <v>-21.319796954314</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.582633053221</v>
+        <v>-56.697009102730</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I20" s="15">
         <v>7</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="L20" s="14">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.039215686274</v>
+        <v>-98.143236074270</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.793103448275</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.316546762589</v>
+        <v>-8.391608391608</v>
       </c>
       <c r="I21" s="17">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="J21" s="17">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="K21" s="18">
-        <v>0.191938579654</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>20.276497695852</v>
+        <v>23.194748358862</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.532062391681</v>
+        <v>-8.603896103896</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.829465731246</v>
+        <v>-71.565656565656</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I22" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="15">
         <v>28</v>
       </c>
       <c r="K22" s="14">
-        <v>3.571428571428</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L22" s="14">
-        <v>52.631578947368</v>
+        <v>57.894736842105</v>
       </c>
       <c r="M22" s="14">
-        <v>20.833333333333</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D24" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" s="14">
-        <v>31.578947368421</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F24" s="15">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="G24" s="15">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="H24" s="14">
-        <v>-2.590673575129</v>
+        <v>-6.214689265536</v>
       </c>
       <c r="I24" s="15">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="J24" s="15">
-        <v>738</v>
+        <v>780</v>
       </c>
       <c r="K24" s="14">
-        <v>14.634146341463</v>
+        <v>11.282051282051</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.870264064293</v>
+        <v>-7.165775401069</v>
       </c>
       <c r="M24" s="14">
-        <v>76.25</v>
+        <v>67.567567567567</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D25" s="15">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E25" s="14">
-        <v>44</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="F25" s="15">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G25" s="15">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H25" s="14">
-        <v>0.671140939597</v>
+        <v>-3.521126760563</v>
       </c>
       <c r="I25" s="15">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="J25" s="15">
-        <v>585</v>
+        <v>623</v>
       </c>
       <c r="K25" s="14">
-        <v>23.931623931623</v>
+        <v>20.064205457463</v>
       </c>
       <c r="L25" s="14">
-        <v>-2.027027027027</v>
+        <v>-5.436156763590</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G26" s="15">
         <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>16.279069767441</v>
+        <v>9.302325581395</v>
       </c>
       <c r="I26" s="15">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J26" s="15">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K26" s="14">
-        <v>-9.554140127388</v>
+        <v>-12.209302325581</v>
       </c>
       <c r="L26" s="14">
-        <v>-8.387096774193</v>
+        <v>-6.790123456790</v>
       </c>
       <c r="M26" s="14">
-        <v>22.413793103448</v>
+        <v>23.770491803278</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>1</v>
+      </c>
+      <c r="G27" s="15">
         <v>2</v>
-      </c>
-      <c r="G27" s="15">
-        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-50</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
         <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="14">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="15">
         <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="15">
+        <v>9</v>
+      </c>
+      <c r="G28" s="15">
         <v>11</v>
       </c>
-      <c r="G28" s="15">
-        <v>9</v>
-      </c>
       <c r="H28" s="14">
-        <v>22.222222222222</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="15">
+        <v>34</v>
+      </c>
+      <c r="J28" s="15">
         <v>32</v>
       </c>
-      <c r="J28" s="15">
-        <v>29</v>
-      </c>
       <c r="K28" s="14">
-        <v>10.344827586206</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M15" s="14">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="N15" s="14">
-        <v>166.666666666667</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="15">
         <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J16" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K16" s="14">
-        <v>-25.581395348837</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="L16" s="14">
-        <v>-21.951219512195</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M16" s="14">
-        <v>-39.622641509434</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.489208633093</v>
+        <v>-88.311688311688</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>-28.571428571428</v>
+        <v>-12</v>
       </c>
       <c r="I17" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J17" s="15">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L17" s="14">
-        <v>30.909090909090</v>
+        <v>29.032258064516</v>
       </c>
       <c r="M17" s="14">
-        <v>118.181818181818</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N17" s="14">
-        <v>-2.702702702702</v>
+        <v>-1.234567901234</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-14.285714285714</v>
+        <v>20</v>
       </c>
       <c r="F18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="15">
         <v>20</v>
       </c>
       <c r="H18" s="14">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="I18" s="15">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J18" s="15">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K18" s="14">
-        <v>-10.483870967741</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L18" s="14">
-        <v>88.135593220339</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M18" s="14">
-        <v>15.625</v>
+        <v>19.387755102040</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.680672268907</v>
+        <v>-77.413127413127</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D19" s="15">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E19" s="14">
-        <v>-11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="15">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G19" s="15">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H19" s="14">
-        <v>6.410256410256</v>
+        <v>-6.097560975609</v>
       </c>
       <c r="I19" s="15">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="J19" s="15">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="K19" s="14">
-        <v>8.116883116883</v>
+        <v>5.757575757575</v>
       </c>
       <c r="L19" s="14">
-        <v>15.224913494809</v>
+        <v>12.580645161290</v>
       </c>
       <c r="M19" s="14">
-        <v>-21.276595744680</v>
+        <v>-22.271714922049</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.697009102730</v>
+        <v>-57.439024390243</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>1</v>
@@ -1128,10 +1128,10 @@
         <v>-30</v>
       </c>
       <c r="M20" s="14">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.143236074270</v>
+        <v>-98.241206030150</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.380952380952</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.391608391608</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="I21" s="17">
-        <v>563</v>
+        <v>598</v>
       </c>
       <c r="J21" s="17">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>-0.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>23.194748358862</v>
+        <v>22.040816326530</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.603896103896</v>
+        <v>-7.858243451463</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.565656565656</v>
+        <v>-71.951219512195</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I22" s="15">
         <v>30</v>
@@ -1207,7 +1207,7 @@
         <v>7.142857142857</v>
       </c>
       <c r="L22" s="14">
-        <v>57.894736842105</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M22" s="14">
         <v>20</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="15">
         <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L23" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M23" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E24" s="14">
-        <v>-42.857142857142</v>
+        <v>6.818181818181</v>
       </c>
       <c r="F24" s="15">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G24" s="15">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H24" s="14">
-        <v>-6.214689265536</v>
+        <v>-4.972375690607</v>
       </c>
       <c r="I24" s="15">
-        <v>868</v>
+        <v>915</v>
       </c>
       <c r="J24" s="15">
-        <v>780</v>
+        <v>824</v>
       </c>
       <c r="K24" s="14">
-        <v>11.282051282051</v>
+        <v>11.043689320388</v>
       </c>
       <c r="L24" s="14">
-        <v>-7.165775401069</v>
+        <v>-8.224674022066</v>
       </c>
       <c r="M24" s="14">
-        <v>67.567567567567</v>
+        <v>66.970802919708</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D25" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E25" s="14">
-        <v>-44.736842105263</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="F25" s="15">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G25" s="15">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H25" s="14">
-        <v>-3.521126760563</v>
+        <v>-8</v>
       </c>
       <c r="I25" s="15">
-        <v>748</v>
+        <v>786</v>
       </c>
       <c r="J25" s="15">
-        <v>623</v>
+        <v>664</v>
       </c>
       <c r="K25" s="14">
-        <v>20.064205457463</v>
+        <v>18.373493975903</v>
       </c>
       <c r="L25" s="14">
-        <v>-5.436156763590</v>
+        <v>-6.761565836298</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>-40</v>
+        <v>260</v>
       </c>
       <c r="F26" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H26" s="14">
-        <v>9.302325581395</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="J26" s="15">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.209302325581</v>
+        <v>-6.214689265536</v>
       </c>
       <c r="L26" s="14">
-        <v>-6.790123456790</v>
+        <v>-4.597701149425</v>
       </c>
       <c r="M26" s="14">
-        <v>23.770491803278</v>
+        <v>26.717557251908</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
+        <v>11</v>
+      </c>
+      <c r="J27" s="15">
         <v>10</v>
       </c>
-      <c r="J27" s="15">
-        <v>9</v>
-      </c>
       <c r="K27" s="14">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L27" s="14">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>5</v>
+      </c>
+      <c r="D28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
       <c r="E28" s="14">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F28" s="15">
         <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
+        <v>39</v>
+      </c>
+      <c r="J28" s="15">
         <v>34</v>
       </c>
-      <c r="J28" s="15">
-        <v>32</v>
-      </c>
       <c r="K28" s="14">
-        <v>6.25</v>
+        <v>14.705882352941</v>
       </c>
       <c r="L28" s="14">
-        <v>-8.108108108108</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
@@ -914,10 +914,10 @@
         <v>9</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="14">
         <v>350</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J16" s="15">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K16" s="14">
-        <v>-23.404255319148</v>
+        <v>-28.070175438596</v>
       </c>
       <c r="L16" s="14">
-        <v>-14.285714285714</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="M16" s="14">
-        <v>-32.075471698113</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.311688311688</v>
+        <v>-87.267080745341</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
         <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>-12</v>
+        <v>16</v>
       </c>
       <c r="I17" s="15">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J17" s="15">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K17" s="14">
-        <v>2.564102564102</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L17" s="14">
-        <v>29.032258064516</v>
+        <v>36.231884057971</v>
       </c>
       <c r="M17" s="14">
-        <v>128.571428571429</v>
+        <v>168.571428571429</v>
       </c>
       <c r="N17" s="14">
-        <v>-1.234567901234</v>
+        <v>11.904761904761</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G18" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>5</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I18" s="15">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J18" s="15">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K18" s="14">
-        <v>-9.302325581395</v>
+        <v>-9.923664122137</v>
       </c>
       <c r="L18" s="14">
-        <v>85.714285714285</v>
+        <v>76.119402985074</v>
       </c>
       <c r="M18" s="14">
-        <v>19.387755102040</v>
+        <v>16.831683168316</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.413127413127</v>
+        <v>-78.427787934186</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="14">
-        <v>-9.090909090909</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="15">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G19" s="15">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H19" s="14">
-        <v>-6.097560975609</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="I19" s="15">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="J19" s="15">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="K19" s="14">
-        <v>5.757575757575</v>
+        <v>2.808988764044</v>
       </c>
       <c r="L19" s="14">
-        <v>12.580645161290</v>
+        <v>11.246200607902</v>
       </c>
       <c r="M19" s="14">
-        <v>-22.271714922049</v>
+        <v>-23.270440251572</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.439024390243</v>
+        <v>-57.540603248259</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>1</v>
@@ -1119,19 +1119,19 @@
         <v>7</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
+        <v>-41.666666666666</v>
+      </c>
+      <c r="L20" s="14">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="M20" s="14">
         <v>-30</v>
       </c>
-      <c r="L20" s="14">
-        <v>-30</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-22.222222222222</v>
-      </c>
       <c r="N20" s="14">
-        <v>-98.241206030150</v>
+        <v>-98.360655737704</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.405405405405</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.344827586206</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I21" s="17">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="J21" s="17">
-        <v>600</v>
+        <v>648</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.333333333333</v>
+        <v>-2.006172839506</v>
       </c>
       <c r="L21" s="18">
-        <v>22.040816326530</v>
+        <v>20.722433460076</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.858243451463</v>
+        <v>-7.434402332361</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.951219512195</v>
+        <v>-71.765228990662</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="I22" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J22" s="15">
         <v>28</v>
       </c>
       <c r="K22" s="14">
-        <v>7.142857142857</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L22" s="14">
-        <v>42.857142857142</v>
+        <v>43.478260869565</v>
       </c>
       <c r="M22" s="14">
-        <v>20</v>
+        <v>17.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <v>9</v>
       </c>
       <c r="J23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
         <v>200</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D24" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>6.818181818181</v>
+        <v>60.869565217391</v>
       </c>
       <c r="F24" s="15">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="G24" s="15">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.972375690607</v>
+        <v>14.705882352941</v>
       </c>
       <c r="I24" s="15">
-        <v>915</v>
+        <v>989</v>
       </c>
       <c r="J24" s="15">
-        <v>824</v>
+        <v>870</v>
       </c>
       <c r="K24" s="14">
-        <v>11.043689320388</v>
+        <v>13.678160919540</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.224674022066</v>
+        <v>-5.449330783938</v>
       </c>
       <c r="M24" s="14">
-        <v>66.970802919708</v>
+        <v>71.403812824956</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D25" s="15">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>-7.317073170731</v>
+        <v>17.777777777777</v>
       </c>
       <c r="F25" s="15">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="G25" s="15">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H25" s="14">
-        <v>-8</v>
+        <v>1.342281879194</v>
       </c>
       <c r="I25" s="15">
-        <v>786</v>
+        <v>839</v>
       </c>
       <c r="J25" s="15">
-        <v>664</v>
+        <v>709</v>
       </c>
       <c r="K25" s="14">
-        <v>18.373493975903</v>
+        <v>18.335684062059</v>
       </c>
       <c r="L25" s="14">
-        <v>-6.761565836298</v>
+        <v>-5.411499436302</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>260</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H26" s="14">
-        <v>33.333333333333</v>
+        <v>27.5</v>
       </c>
       <c r="I26" s="15">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="J26" s="15">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K26" s="14">
-        <v>-6.214689265536</v>
+        <v>-7.253886010362</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.597701149425</v>
+        <v>-3.243243243243</v>
       </c>
       <c r="M26" s="14">
-        <v>26.717557251908</v>
+        <v>25.174825174825</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
+        <v>12</v>
+      </c>
+      <c r="J27" s="15">
         <v>11</v>
       </c>
-      <c r="J27" s="15">
-        <v>10</v>
-      </c>
       <c r="K27" s="14">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L27" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
         <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I28" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J28" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K28" s="14">
-        <v>14.705882352941</v>
+        <v>2.5</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-013pct.xlsx
+++ b/data/source/weekly/cs-en-us-013pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,260 +878,260 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="E15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
+        <v>9</v>
+      </c>
+      <c r="K15" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L15" s="15">
+        <v>400</v>
+      </c>
+      <c r="M15" s="15">
         <v>100</v>
       </c>
-      <c r="I15" s="15">
-        <v>9</v>
-      </c>
-      <c r="J15" s="15">
-        <v>7</v>
-      </c>
-      <c r="K15" s="14">
-        <v>28.571428571428</v>
-      </c>
-      <c r="L15" s="14">
-        <v>350</v>
-      </c>
-      <c r="M15" s="14">
-        <v>80</v>
-      </c>
-      <c r="N15" s="14">
-        <v>125</v>
+      <c r="N15" s="15">
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>5</v>
-      </c>
-      <c r="D16" s="15">
-        <v>10</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F16" s="15">
-        <v>12</v>
-      </c>
-      <c r="G16" s="15">
-        <v>18</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I16" s="15">
-        <v>41</v>
-      </c>
-      <c r="J16" s="15">
-        <v>57</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-28.070175438596</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-12.765957446808</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-29.310344827586</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-87.267080745341</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-85.714285714285</v>
+      </c>
+      <c r="F16" s="14">
+        <v>11</v>
+      </c>
+      <c r="G16" s="14">
+        <v>23</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-52.173913043478</v>
+      </c>
+      <c r="I16" s="14">
+        <v>42</v>
+      </c>
+      <c r="J16" s="14">
+        <v>64</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-34.375</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-30</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-87.790697674418</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>12</v>
-      </c>
-      <c r="D17" s="15">
-        <v>7</v>
-      </c>
-      <c r="E17" s="14">
-        <v>71.428571428571</v>
-      </c>
-      <c r="F17" s="15">
-        <v>29</v>
-      </c>
-      <c r="G17" s="15">
-        <v>25</v>
-      </c>
-      <c r="H17" s="14">
-        <v>16</v>
-      </c>
-      <c r="I17" s="15">
-        <v>94</v>
-      </c>
-      <c r="J17" s="15">
-        <v>85</v>
-      </c>
-      <c r="K17" s="14">
-        <v>10.588235294117</v>
-      </c>
-      <c r="L17" s="14">
-        <v>36.231884057971</v>
-      </c>
-      <c r="M17" s="14">
-        <v>168.571428571429</v>
-      </c>
-      <c r="N17" s="14">
-        <v>11.904761904761</v>
+      <c r="C17" s="14">
+        <v>9</v>
+      </c>
+      <c r="D17" s="14">
+        <v>4</v>
+      </c>
+      <c r="E17" s="15">
+        <v>125</v>
+      </c>
+      <c r="F17" s="14">
+        <v>35</v>
+      </c>
+      <c r="G17" s="14">
+        <v>22</v>
+      </c>
+      <c r="H17" s="15">
+        <v>59.090909090909</v>
+      </c>
+      <c r="I17" s="14">
+        <v>103</v>
+      </c>
+      <c r="J17" s="14">
+        <v>89</v>
+      </c>
+      <c r="K17" s="15">
+        <v>15.730337078651</v>
+      </c>
+      <c r="L17" s="15">
+        <v>35.526315789473</v>
+      </c>
+      <c r="M17" s="15">
+        <v>157.5</v>
+      </c>
+      <c r="N17" s="15">
+        <v>14.444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>18</v>
-      </c>
-      <c r="G18" s="15">
-        <v>17</v>
-      </c>
-      <c r="H18" s="14">
-        <v>5.882352941176</v>
-      </c>
-      <c r="I18" s="15">
-        <v>118</v>
-      </c>
-      <c r="J18" s="15">
-        <v>131</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-9.923664122137</v>
-      </c>
-      <c r="L18" s="14">
-        <v>76.119402985074</v>
-      </c>
-      <c r="M18" s="14">
-        <v>16.831683168316</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-78.427787934186</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>15</v>
+      </c>
+      <c r="G18" s="14">
+        <v>16</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-6.25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>120</v>
+      </c>
+      <c r="J18" s="14">
+        <v>133</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-9.774436090225</v>
+      </c>
+      <c r="L18" s="15">
+        <v>73.913043478260</v>
+      </c>
+      <c r="M18" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-78.984238178634</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>18</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
         <v>26</v>
       </c>
-      <c r="E19" s="14">
-        <v>-30.769230769230</v>
-      </c>
-      <c r="F19" s="15">
-        <v>74</v>
-      </c>
-      <c r="G19" s="15">
-        <v>90</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-17.777777777777</v>
-      </c>
-      <c r="I19" s="15">
-        <v>366</v>
-      </c>
-      <c r="J19" s="15">
-        <v>356</v>
-      </c>
-      <c r="K19" s="14">
-        <v>2.808988764044</v>
-      </c>
-      <c r="L19" s="14">
-        <v>11.246200607902</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-23.270440251572</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-57.540603248259</v>
+      <c r="D19" s="14">
+        <v>26</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>84</v>
+      </c>
+      <c r="G19" s="14">
+        <v>101</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-16.831683168316</v>
+      </c>
+      <c r="I19" s="14">
+        <v>392</v>
+      </c>
+      <c r="J19" s="14">
+        <v>382</v>
+      </c>
+      <c r="K19" s="15">
+        <v>2.617801047120</v>
+      </c>
+      <c r="L19" s="15">
+        <v>12</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-22.682445759368</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-56.637168141592</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="G20" s="15">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-80</v>
-      </c>
-      <c r="I20" s="15">
-        <v>7</v>
-      </c>
-      <c r="J20" s="15">
-        <v>12</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-36.363636363636</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-30</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-98.360655737704</v>
+      <c r="E20" s="15">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I20" s="14">
+        <v>9</v>
+      </c>
+      <c r="J20" s="14">
+        <v>13</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-30.769230769230</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-10</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-97.991071428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.820512820512</v>
+        <v>-10.650887573964</v>
       </c>
       <c r="I21" s="17">
-        <v>635</v>
+        <v>677</v>
       </c>
       <c r="J21" s="17">
-        <v>648</v>
+        <v>690</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.006172839506</v>
+        <v>-1.884057971014</v>
       </c>
       <c r="L21" s="18">
-        <v>20.722433460076</v>
+        <v>21.326164874552</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.434402332361</v>
+        <v>-7.260273972602</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.765228990662</v>
+        <v>-71.362098138747</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>3</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>6</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>500</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="14">
         <v>33</v>
       </c>
-      <c r="J22" s="15">
-        <v>28</v>
-      </c>
-      <c r="K22" s="14">
-        <v>17.857142857142</v>
-      </c>
-      <c r="L22" s="14">
-        <v>43.478260869565</v>
-      </c>
-      <c r="M22" s="14">
-        <v>17.857142857142</v>
+      <c r="J22" s="14">
+        <v>30</v>
+      </c>
+      <c r="K22" s="15">
+        <v>10</v>
+      </c>
+      <c r="L22" s="15">
+        <v>32</v>
+      </c>
+      <c r="M22" s="15">
+        <v>13.793103448275</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
+      <c r="E23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="15">
-        <v>9</v>
-      </c>
-      <c r="J23" s="15">
-        <v>9</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
+        <v>2</v>
+      </c>
+      <c r="H23" s="15">
         <v>0</v>
       </c>
-      <c r="L23" s="14">
-        <v>200</v>
-      </c>
-      <c r="M23" s="14">
-        <v>50</v>
+      <c r="I23" s="14">
+        <v>10</v>
+      </c>
+      <c r="J23" s="14">
+        <v>10</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>233.333333333333</v>
+      </c>
+      <c r="M23" s="15">
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>74</v>
-      </c>
-      <c r="D24" s="15">
-        <v>46</v>
-      </c>
-      <c r="E24" s="14">
-        <v>60.869565217391</v>
-      </c>
-      <c r="F24" s="15">
-        <v>195</v>
-      </c>
-      <c r="G24" s="15">
-        <v>170</v>
-      </c>
-      <c r="H24" s="14">
-        <v>14.705882352941</v>
-      </c>
-      <c r="I24" s="15">
-        <v>989</v>
-      </c>
-      <c r="J24" s="15">
-        <v>870</v>
-      </c>
-      <c r="K24" s="14">
-        <v>13.678160919540</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-5.449330783938</v>
-      </c>
-      <c r="M24" s="14">
-        <v>71.403812824956</v>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>52</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="F24" s="14">
+        <v>184</v>
+      </c>
+      <c r="G24" s="14">
+        <v>184</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1028</v>
+      </c>
+      <c r="J24" s="14">
+        <v>922</v>
+      </c>
+      <c r="K24" s="15">
+        <v>11.496746203904</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-6.460418562329</v>
+      </c>
+      <c r="M24" s="15">
+        <v>69.078947368421</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>53</v>
-      </c>
-      <c r="D25" s="15">
-        <v>45</v>
-      </c>
-      <c r="E25" s="14">
-        <v>17.777777777777</v>
-      </c>
-      <c r="F25" s="15">
-        <v>151</v>
-      </c>
-      <c r="G25" s="15">
-        <v>149</v>
-      </c>
-      <c r="H25" s="14">
-        <v>1.342281879194</v>
-      </c>
-      <c r="I25" s="15">
-        <v>839</v>
-      </c>
-      <c r="J25" s="15">
-        <v>709</v>
-      </c>
-      <c r="K25" s="14">
-        <v>18.335684062059</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-5.411499436302</v>
+      <c r="C25" s="14">
+        <v>32</v>
+      </c>
+      <c r="D25" s="14">
+        <v>38</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-15.789473684210</v>
+      </c>
+      <c r="F25" s="14">
+        <v>144</v>
+      </c>
+      <c r="G25" s="14">
+        <v>162</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="I25" s="14">
+        <v>871</v>
+      </c>
+      <c r="J25" s="14">
+        <v>747</v>
+      </c>
+      <c r="K25" s="15">
+        <v>16.599732262382</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-6.344086021505</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>14</v>
-      </c>
-      <c r="D26" s="15">
-        <v>16</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="F26" s="15">
+      <c r="C26" s="14">
+        <v>12</v>
+      </c>
+      <c r="D26" s="14">
+        <v>12</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
         <v>51</v>
       </c>
-      <c r="G26" s="15">
-        <v>40</v>
-      </c>
-      <c r="H26" s="14">
-        <v>27.5</v>
-      </c>
-      <c r="I26" s="15">
-        <v>179</v>
-      </c>
-      <c r="J26" s="15">
-        <v>193</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-7.253886010362</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-3.243243243243</v>
-      </c>
-      <c r="M26" s="14">
-        <v>25.174825174825</v>
+      <c r="G26" s="14">
+        <v>48</v>
+      </c>
+      <c r="H26" s="15">
+        <v>6.25</v>
+      </c>
+      <c r="I26" s="14">
+        <v>191</v>
+      </c>
+      <c r="J26" s="14">
+        <v>205</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-6.829268292682</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-3.045685279187</v>
+      </c>
+      <c r="M26" s="15">
+        <v>26.490066225165</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>50</v>
-      </c>
-      <c r="I27" s="15">
-        <v>12</v>
-      </c>
-      <c r="J27" s="15">
-        <v>11</v>
-      </c>
-      <c r="K27" s="14">
-        <v>9.090909090909</v>
-      </c>
-      <c r="L27" s="14">
-        <v>200</v>
+      <c r="I27" s="14">
+        <v>13</v>
+      </c>
+      <c r="J27" s="14">
+        <v>13</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>225</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>6</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F28" s="15">
-        <v>9</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
         <v>14</v>
       </c>
-      <c r="H28" s="14">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="I28" s="15">
-        <v>41</v>
-      </c>
-      <c r="J28" s="15">
-        <v>40</v>
-      </c>
-      <c r="K28" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-2.380952380952</v>
+      <c r="G28" s="14">
+        <v>16</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="I28" s="14">
+        <v>46</v>
+      </c>
+      <c r="J28" s="14">
+        <v>45</v>
+      </c>
+      <c r="K28" s="15">
+        <v>2.222222222222</v>
+      </c>
+      <c r="L28" s="15">
+        <v>9.523809523809</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1484,7 +1484,7 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
@@ -1493,14 +1493,14 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
-        <v>-66.666666666666</v>
+      <c r="N29" s="15">
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1525,7 +1525,7 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
@@ -1534,14 +1534,14 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
-        <v>-66.666666666666</v>
+      <c r="N30" s="15">
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,25 +1557,25 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
-      </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>0</v>
-      </c>
-      <c r="I31" s="15">
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>5</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="15">
         <v>-40</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>-25</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>13</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>6</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>2</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>2</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>2</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>0</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>0</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-84.615384615384</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
-        <v>21</v>
-      </c>
-      <c r="E40" s="15">
-        <v>21</v>
-      </c>
-      <c r="G40" s="15">
+      <c r="C40" s="14">
+        <v>21</v>
+      </c>
+      <c r="E40" s="14">
+        <v>21</v>
+      </c>
+      <c r="G40" s="14">
         <v>7</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>10</v>
       </c>
-      <c r="J40" s="15">
-        <v>20</v>
-      </c>
-      <c r="K40" s="14">
+      <c r="J40" s="14">
+        <v>20</v>
+      </c>
+      <c r="K40" s="15">
         <v>100</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>185.714285714286</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-4.761904761904</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-4.761904761904</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1319</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1050</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>433</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>308</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>190</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-38.311688311688</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-56.120092378752</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-81.904761904761</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-85.595147839272</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>357</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>303</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>205</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>177</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>284</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>60.451977401129</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>38.536585365853</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-6.270627062706</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-20.448179271708</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1986</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1649</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>692</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>552</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>380</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-31.159420289855</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-45.086705202312</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-76.955730745906</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-80.866062437059</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>4632</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>2765</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>1878</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>1753</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>1250</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-28.693667997718</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-33.439829605963</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-54.792043399638</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-73.013816925734</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1812</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>1286</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>444</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>216</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>53</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-75.462962962963</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-88.063063063063</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-95.878693623639</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-97.075055187638</v>
       </c>
     </row>
